--- a/artfynd/A 28451-2026 artfynd.xlsx
+++ b/artfynd/A 28451-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150258</v>
+        <v>134665271</v>
       </c>
       <c r="B4" t="n">
-        <v>106229</v>
+        <v>101301</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Röd trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Actaea erythrocarpa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fisch.) Kom.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,13 +926,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777930</v>
+        <v>777929</v>
       </c>
       <c r="R4" t="n">
-        <v>7380460</v>
+        <v>7380461</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113888836</v>
+        <v>134665272</v>
       </c>
       <c r="B5" t="n">
-        <v>97989</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,13 +1032,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777772</v>
+        <v>777891</v>
       </c>
       <c r="R5" t="n">
-        <v>7380420</v>
+        <v>7380445</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1096,6 +1096,218 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121150258</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Randaträsk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>777930</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7380460</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113888836</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Randaträsk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>777772</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7380420</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28451-2026 artfynd.xlsx
+++ b/artfynd/A 28451-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150245</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150246</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665271</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665272</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150258</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,8 +1338,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888836</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>